--- a/CPRG-305-B/group-assignment-3/DealerOps_Group_Assignment_3_Defect_Tracking.xlsx
+++ b/CPRG-305-B/group-assignment-3/DealerOps_Group_Assignment_3_Defect_Tracking.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Log" sheetId="1" r:id="Rb57da6dd237f448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Tracking" sheetId="2" r:id="Re51c3e5911684040"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progress" sheetId="3" r:id="Rd94db0e6b354444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Log" sheetId="1" r:id="R39a97faf62d44cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Tracking" sheetId="2" r:id="R66e0c2f7c9ad425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progress" sheetId="3" r:id="R943b9801c38f4167"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1497,7 +1497,7 @@
         <x:v>Execute integration case 1</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1506,10 +1506,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
         <x:v>High</x:v>
@@ -1527,7 +1527,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P23" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1547,7 +1547,7 @@
         <x:v>Execute integration case 2</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1556,10 +1556,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
         <x:v>High</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P24" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1597,7 +1597,7 @@
         <x:v>Execute integration case 3</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1606,10 +1606,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
         <x:v>High</x:v>
@@ -1627,7 +1627,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P25" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1647,7 +1647,7 @@
         <x:v>Execute integration case 4</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1656,10 +1656,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
         <x:v>High</x:v>
@@ -1677,7 +1677,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P26" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1697,7 +1697,7 @@
         <x:v>Execute integration case 5</x:v>
       </x:c>
       <x:c r="F27" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1706,10 +1706,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
         <x:v>High</x:v>
@@ -1727,7 +1727,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P27" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1747,7 +1747,7 @@
         <x:v>Execute integration case 6</x:v>
       </x:c>
       <x:c r="F28" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1756,10 +1756,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
         <x:v>High</x:v>
@@ -1777,7 +1777,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P28" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1797,7 +1797,7 @@
         <x:v>Execute integration case 7</x:v>
       </x:c>
       <x:c r="F29" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1806,10 +1806,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
         <x:v>High</x:v>
@@ -1827,7 +1827,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P29" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1847,7 +1847,7 @@
         <x:v>Execute integration case 8</x:v>
       </x:c>
       <x:c r="F30" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G30" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1856,10 +1856,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
         <x:v>High</x:v>
@@ -1877,7 +1877,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P30" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1897,7 +1897,7 @@
         <x:v>Execute integration case 9</x:v>
       </x:c>
       <x:c r="F31" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1906,10 +1906,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
         <x:v>High</x:v>
@@ -1927,7 +1927,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P31" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1947,7 +1947,7 @@
         <x:v>Execute integration case 10</x:v>
       </x:c>
       <x:c r="F32" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -1956,10 +1956,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str">
         <x:v>High</x:v>
@@ -1977,7 +1977,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P32" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1997,7 +1997,7 @@
         <x:v>Execute integration case 11</x:v>
       </x:c>
       <x:c r="F33" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2006,10 +2006,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str">
         <x:v>High</x:v>
@@ -2027,7 +2027,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P33" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2047,7 +2047,7 @@
         <x:v>Execute integration case 12</x:v>
       </x:c>
       <x:c r="F34" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2056,10 +2056,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str">
         <x:v>High</x:v>
@@ -2077,7 +2077,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P34" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2097,7 +2097,7 @@
         <x:v>Execute integration case 13</x:v>
       </x:c>
       <x:c r="F35" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2106,10 +2106,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str">
         <x:v>High</x:v>
@@ -2127,7 +2127,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P35" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2147,7 +2147,7 @@
         <x:v>Execute integration case 14</x:v>
       </x:c>
       <x:c r="F36" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2156,10 +2156,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K36" s="10" t="str">
         <x:v>High</x:v>
@@ -2177,7 +2177,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P36" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2197,7 +2197,7 @@
         <x:v>Execute integration case 15</x:v>
       </x:c>
       <x:c r="F37" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2206,10 +2206,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K37" s="10" t="str">
         <x:v>High</x:v>
@@ -2227,7 +2227,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P37" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2247,7 +2247,7 @@
         <x:v>Execute integration case 16</x:v>
       </x:c>
       <x:c r="F38" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2256,10 +2256,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K38" s="10" t="str">
         <x:v>High</x:v>
@@ -2277,7 +2277,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P38" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2297,7 +2297,7 @@
         <x:v>Execute integration case 17</x:v>
       </x:c>
       <x:c r="F39" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G39" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2306,10 +2306,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str">
         <x:v>High</x:v>
@@ -2327,7 +2327,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P39" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2347,7 +2347,7 @@
         <x:v>Execute integration case 18</x:v>
       </x:c>
       <x:c r="F40" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G40" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2356,10 +2356,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K40" s="10" t="str">
         <x:v>High</x:v>
@@ -2377,7 +2377,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P40" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2397,7 +2397,7 @@
         <x:v>Execute integration case 19</x:v>
       </x:c>
       <x:c r="F41" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G41" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2406,10 +2406,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J41" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K41" s="10" t="str">
         <x:v>High</x:v>
@@ -2427,7 +2427,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P41" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2447,7 +2447,7 @@
         <x:v>Execute integration case 20</x:v>
       </x:c>
       <x:c r="F42" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G42" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2456,10 +2456,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J42" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K42" s="10" t="str">
         <x:v>High</x:v>
@@ -2477,7 +2477,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P42" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2497,7 +2497,7 @@
         <x:v>Execute integration case 21</x:v>
       </x:c>
       <x:c r="F43" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G43" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2506,10 +2506,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J43" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K43" s="10" t="str">
         <x:v>High</x:v>
@@ -2527,7 +2527,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P43" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2547,7 +2547,7 @@
         <x:v>Execute integration case 22</x:v>
       </x:c>
       <x:c r="F44" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G44" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2556,10 +2556,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J44" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K44" s="10" t="str">
         <x:v>High</x:v>
@@ -2577,7 +2577,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P44" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2597,7 +2597,7 @@
         <x:v>Execute integration case 23</x:v>
       </x:c>
       <x:c r="F45" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G45" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2606,10 +2606,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J45" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K45" s="10" t="str">
         <x:v>High</x:v>
@@ -2627,7 +2627,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P45" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -2647,7 +2647,7 @@
         <x:v>Execute integration case 24</x:v>
       </x:c>
       <x:c r="F46" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G46" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2656,10 +2656,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I46" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J46" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K46" s="10" t="str">
         <x:v>High</x:v>
@@ -2677,7 +2677,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P46" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -2697,7 +2697,7 @@
         <x:v>Execute integration case 25</x:v>
       </x:c>
       <x:c r="F47" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G47" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2706,10 +2706,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I47" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J47" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K47" s="10" t="str">
         <x:v>High</x:v>
@@ -2727,7 +2727,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P47" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -2747,7 +2747,7 @@
         <x:v>Execute integration case 26</x:v>
       </x:c>
       <x:c r="F48" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G48" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2756,10 +2756,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I48" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J48" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K48" s="10" t="str">
         <x:v>High</x:v>
@@ -2777,7 +2777,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P48" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -2797,7 +2797,7 @@
         <x:v>Execute integration case 27</x:v>
       </x:c>
       <x:c r="F49" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G49" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2806,10 +2806,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I49" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J49" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K49" s="10" t="str">
         <x:v>High</x:v>
@@ -2827,7 +2827,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P49" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -2847,7 +2847,7 @@
         <x:v>Execute integration case 28</x:v>
       </x:c>
       <x:c r="F50" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G50" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2856,10 +2856,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I50" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J50" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K50" s="10" t="str">
         <x:v>High</x:v>
@@ -2877,7 +2877,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P50" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -2897,7 +2897,7 @@
         <x:v>Execute integration case 29</x:v>
       </x:c>
       <x:c r="F51" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G51" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2906,10 +2906,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I51" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J51" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K51" s="10" t="str">
         <x:v>High</x:v>
@@ -2927,7 +2927,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P51" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -2947,7 +2947,7 @@
         <x:v>Execute integration case 30</x:v>
       </x:c>
       <x:c r="F52" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G52" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -2956,10 +2956,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I52" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J52" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K52" s="10" t="str">
         <x:v>High</x:v>
@@ -2977,7 +2977,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P52" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -2997,7 +2997,7 @@
         <x:v>Execute integration case 31</x:v>
       </x:c>
       <x:c r="F53" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G53" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3006,10 +3006,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I53" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J53" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K53" s="10" t="str">
         <x:v>High</x:v>
@@ -3027,7 +3027,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P53" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -3047,7 +3047,7 @@
         <x:v>Execute integration case 32</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G54" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3056,10 +3056,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J54" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K54" s="10" t="str">
         <x:v>High</x:v>
@@ -3077,7 +3077,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P54" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -3097,7 +3097,7 @@
         <x:v>Execute integration case 33</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3106,10 +3106,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J55" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K55" s="10" t="str">
         <x:v>High</x:v>
@@ -3127,7 +3127,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P55" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -3147,7 +3147,7 @@
         <x:v>Execute integration case 34</x:v>
       </x:c>
       <x:c r="F56" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3156,10 +3156,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J56" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K56" s="10" t="str">
         <x:v>High</x:v>
@@ -3177,7 +3177,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P56" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -3197,7 +3197,7 @@
         <x:v>Execute integration case 35</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3206,10 +3206,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J57" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K57" s="10" t="str">
         <x:v>High</x:v>
@@ -3227,7 +3227,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P57" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -3247,7 +3247,7 @@
         <x:v>Execute integration case 36</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G58" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3256,10 +3256,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J58" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K58" s="10" t="str">
         <x:v>High</x:v>
@@ -3277,7 +3277,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P58" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -3297,7 +3297,7 @@
         <x:v>Execute integration case 37</x:v>
       </x:c>
       <x:c r="F59" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G59" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3306,10 +3306,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I59" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J59" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K59" s="10" t="str">
         <x:v>High</x:v>
@@ -3327,7 +3327,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P59" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -3347,7 +3347,7 @@
         <x:v>Execute integration case 38</x:v>
       </x:c>
       <x:c r="F60" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G60" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3356,10 +3356,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I60" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J60" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K60" s="10" t="str">
         <x:v>High</x:v>
@@ -3377,7 +3377,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P60" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -3397,7 +3397,7 @@
         <x:v>Execute integration case 39</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3406,10 +3406,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I61" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J61" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K61" s="10" t="str">
         <x:v>High</x:v>
@@ -3427,7 +3427,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P61" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -3447,7 +3447,7 @@
         <x:v>Execute integration case 40</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3456,10 +3456,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I62" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J62" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K62" s="10" t="str">
         <x:v>High</x:v>
@@ -3477,7 +3477,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P62" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -3497,7 +3497,7 @@
         <x:v>Execute integration case 41</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G63" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3506,10 +3506,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I63" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J63" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K63" s="10" t="str">
         <x:v>High</x:v>
@@ -3527,7 +3527,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P63" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -3547,7 +3547,7 @@
         <x:v>Execute integration case 42</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G64" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3556,10 +3556,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I64" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J64" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K64" s="10" t="str">
         <x:v>High</x:v>
@@ -3577,7 +3577,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P64" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -3597,7 +3597,7 @@
         <x:v>Execute integration case 43</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G65" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3606,10 +3606,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I65" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J65" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K65" s="10" t="str">
         <x:v>High</x:v>
@@ -3627,7 +3627,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P65" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -3647,7 +3647,7 @@
         <x:v>Execute integration case 44</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G66" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3656,10 +3656,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I66" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J66" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K66" s="10" t="str">
         <x:v>High</x:v>
@@ -3677,7 +3677,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P66" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -3697,7 +3697,7 @@
         <x:v>Execute integration case 45</x:v>
       </x:c>
       <x:c r="F67" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G67" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3706,10 +3706,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I67" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J67" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K67" s="10" t="str">
         <x:v>High</x:v>
@@ -3727,7 +3727,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P67" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -3747,7 +3747,7 @@
         <x:v>Execute integration case 46</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
-        <x:v>Docker engine available; Testcontainers configuration required</x:v>
+        <x:v>Docker Desktop available; Testcontainers API compatibility configured</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
         <x:v>Run mapped integration test against isolated MySQL and services</x:v>
@@ -3756,10 +3756,10 @@
         <x:v>Expected API/persistence/security result</x:v>
       </x:c>
       <x:c r="I68" s="10" t="str">
-        <x:v>Testcontainers did not discover Docker from Maven JVM</x:v>
+        <x:v>Existing core Failsafe integration suite passed; 44 execution targets completed</x:v>
       </x:c>
       <x:c r="J68" s="10" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS / RETEST</x:v>
       </x:c>
       <x:c r="K68" s="10" t="str">
         <x:v>High</x:v>
@@ -3777,7 +3777,7 @@
         <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="P68" s="10" t="str">
-        <x:v>DEF-001; rerun after Docker client discovery is corrected.</x:v>
+        <x:v>DEF-001 retest passed with Java 21, Docker Desktop 29.5.3, DOCKER_HOST Unix socket, and user-level docker-java API 1.44 compatibility setting.</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -4919,7 +4919,7 @@
         <x:v>dealer-core / Testcontainers</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>Testcontainers could not discover a valid Docker environment from the Maven JVM; integration batch did not start</x:v>
+        <x:v>Testcontainers Docker API compatibility initially blocked the core integration batch</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
         <x:v>S2 – High</x:v>
@@ -4928,7 +4928,7 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
-        <x:v>Open / environment blocker</x:v>
+        <x:v>Closed / environment corrected</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
         <x:v>Yuandong Yang</x:v>
@@ -4940,17 +4940,19 @@
         <x:v>Development / environment owner</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>Docker client discovery / Unix socket strategy returned an invalid environment</x:v>
+        <x:v>Docker Desktop 29 exposes API 1.54 while the project client default negotiated an incompatible API request</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
-        <x:v>Configure supported Docker client/socket and rerun core IT batch</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str"/>
+        <x:v>Configured the local Docker socket and docker-java API 1.44 compatibility setting, then reran the core Failsafe suite with JWT_MODE=dev</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="str">
+        <x:v>2026-10-13</x:v>
+      </x:c>
       <x:c r="N2" s="10" t="str">
-        <x:v>N</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="O2" s="10" t="str">
-        <x:v>Reproduced with Java 21 and the Docker Desktop Unix socket; a docker-java 3.4.2 compatibility override still returned HTTP 400. Manual containers were healthy.</x:v>
+        <x:v>Retest passed: Docker Desktop 29.5.3 connected, Ryuk and MySQL containers started, Flyway applied 13 migrations, and 44 tests passed with 0 failures, 0 errors, and 0 skipped.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5173,10 +5175,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I2" s="16" t="n">
         <x:f>D2/C2</x:f>
@@ -5191,7 +5193,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
-        <x:v>49 unit methods + 7 container smoke checks + 20 performance requests; formal denominator excludes separate lafe browser smoke and supplemental AI provider verification. DMS/CRM/Assistant data-match passed, live provider follow-up passed, and formal UAT remains.</x:v>
+        <x:v>Original formal denominator remains 87 planned / 76 executed for the baseline evidence set. DEF-001 was closed by a separate Testcontainers retest: 44 Failsafe targets passed with 0 failures. Browser UAT remains intentionally out of scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
